--- a/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-301_CALIFICADO.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO BUENAVISTA (IED)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BUENAVISTA-(IED)-301_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -962,7 +954,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1149,11 +1141,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1161,7 +1149,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1352,11 +1340,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1364,7 +1348,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1555,11 +1539,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1567,7 +1547,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1758,11 +1738,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1770,7 +1746,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1961,11 +1937,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -1973,7 +1945,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2164,11 +2136,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2176,7 +2144,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2367,11 +2335,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2379,7 +2343,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2570,11 +2534,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2582,7 +2542,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2773,11 +2733,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2785,7 +2741,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2976,11 +2932,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -2988,7 +2940,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3179,11 +3131,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3191,7 +3139,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3382,11 +3330,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3394,7 +3338,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3585,11 +3529,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3597,7 +3537,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3788,11 +3728,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -3800,7 +3736,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3991,11 +3927,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4003,7 +3935,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4194,11 +4126,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4206,7 +4134,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4369,11 +4297,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4381,7 +4305,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4572,11 +4496,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4584,7 +4504,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4775,11 +4695,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4787,7 +4703,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4978,11 +4894,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -4990,7 +4902,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5181,11 +5093,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5193,7 +5101,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5384,11 +5292,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5396,7 +5300,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5583,11 +5487,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5595,7 +5495,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5786,11 +5686,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -5798,7 +5694,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5989,11 +5885,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6001,7 +5893,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6192,11 +6084,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6204,7 +6092,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6379,11 +6267,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6391,7 +6275,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6582,11 +6466,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6594,7 +6474,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6785,11 +6665,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -6797,7 +6673,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -6988,11 +6864,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7000,7 +6872,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7191,11 +7063,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7203,7 +7071,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7394,11 +7262,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7406,7 +7270,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7597,11 +7461,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7609,7 +7469,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7784,11 +7644,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7796,7 +7652,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7987,11 +7843,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -7999,7 +7851,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8190,11 +8042,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8202,7 +8050,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8389,11 +8237,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8401,7 +8245,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8584,11 +8428,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8596,7 +8436,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8787,11 +8627,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -8799,7 +8635,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -8990,11 +8826,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9002,7 +8834,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9193,11 +9025,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9205,7 +9033,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9396,11 +9224,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9408,7 +9232,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9599,11 +9423,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9611,7 +9431,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9802,11 +9622,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -9814,7 +9630,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10005,11 +9821,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10017,7 +9829,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10208,11 +10020,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10220,7 +10028,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10407,11 +10215,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10419,7 +10223,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10610,11 +10414,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10622,7 +10422,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10813,11 +10613,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -10825,7 +10621,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11016,11 +10812,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11028,7 +10820,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11219,11 +11011,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11231,7 +11019,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11422,11 +11210,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11434,7 +11218,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11625,11 +11409,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11637,7 +11417,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11828,11 +11608,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -11840,7 +11616,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12003,11 +11779,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12015,7 +11787,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12206,11 +11978,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12218,7 +11986,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12409,11 +12177,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12421,7 +12185,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12612,11 +12376,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12624,7 +12384,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12815,11 +12575,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -12827,7 +12583,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13018,11 +12774,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13030,7 +12782,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13221,11 +12973,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13233,7 +12981,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13424,11 +13172,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13436,7 +13180,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13627,11 +13371,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13639,7 +13379,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13830,11 +13570,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -13842,7 +13578,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14025,11 +13761,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14037,7 +13769,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14216,11 +13948,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14228,7 +13956,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14419,11 +14147,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14431,7 +14155,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14622,11 +14346,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14634,7 +14354,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14825,11 +14545,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -14837,7 +14553,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15028,11 +14744,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15040,7 +14752,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -15231,11 +14943,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15243,7 +14951,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -15414,11 +15122,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15426,7 +15130,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -15617,11 +15321,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15629,7 +15329,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -15820,11 +15520,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001100013</t>
@@ -15832,7 +15528,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BUENAVISTA (IED)</t>
+          <t>COLEGIO BUENAVISTA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
